--- a/data/ams_weekly_data/Tonor/ads_report_week10.xlsx
+++ b/data/ams_weekly_data/Tonor/ads_report_week10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\ams_weekly_data\Tonor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6F6BA00-C39C-4702-B1E2-048E08E346F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C16D5D52-F5AE-4162-AA0A-AC93F22FDF30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{C2EB3544-0B30-4B5A-9817-98DE85FBF6BC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C2EB3544-0B30-4B5A-9817-98DE85FBF6BC}"/>
   </bookViews>
   <sheets>
     <sheet name="SP" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2415" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2471" uniqueCount="82">
   <si>
     <t>Brand</t>
   </si>
@@ -280,6 +280,15 @@
   </si>
   <si>
     <t>B07JMYG6LF</t>
+  </si>
+  <si>
+    <t>Ton_Condenser_TC-777_SBV_KT</t>
+  </si>
+  <si>
+    <t>Ton_Dynamic_K1_SBV_KT</t>
+  </si>
+  <si>
+    <t>B0DFMMTWLY</t>
   </si>
 </sst>
 </file>
@@ -639,7 +648,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51EF6D63-3663-4E20-A7FC-263D078FDDB8}">
-  <dimension ref="A1:I365"/>
+  <dimension ref="A1:I379"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="21.88671875" customWidth="1"/>
@@ -11227,6 +11236,412 @@
         <v>0</v>
       </c>
       <c r="I365" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="366" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A366" t="s">
+        <v>10</v>
+      </c>
+      <c r="B366" t="s">
+        <v>79</v>
+      </c>
+      <c r="C366" t="s">
+        <v>81</v>
+      </c>
+      <c r="D366">
+        <v>245</v>
+      </c>
+      <c r="E366">
+        <v>0</v>
+      </c>
+      <c r="F366">
+        <v>0</v>
+      </c>
+      <c r="G366">
+        <v>0</v>
+      </c>
+      <c r="H366" s="1">
+        <v>0</v>
+      </c>
+      <c r="I366" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="367" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A367" t="s">
+        <v>10</v>
+      </c>
+      <c r="B367" t="s">
+        <v>79</v>
+      </c>
+      <c r="C367" t="s">
+        <v>63</v>
+      </c>
+      <c r="D367">
+        <v>382</v>
+      </c>
+      <c r="E367">
+        <v>1</v>
+      </c>
+      <c r="F367">
+        <v>2</v>
+      </c>
+      <c r="G367">
+        <v>0</v>
+      </c>
+      <c r="H367" s="1">
+        <v>0</v>
+      </c>
+      <c r="I367" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="368" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A368" t="s">
+        <v>10</v>
+      </c>
+      <c r="B368" t="s">
+        <v>79</v>
+      </c>
+      <c r="C368" t="s">
+        <v>63</v>
+      </c>
+      <c r="D368">
+        <v>268</v>
+      </c>
+      <c r="E368">
+        <v>1</v>
+      </c>
+      <c r="F368">
+        <v>8.48</v>
+      </c>
+      <c r="G368">
+        <v>0</v>
+      </c>
+      <c r="H368" s="1">
+        <v>0</v>
+      </c>
+      <c r="I368" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="369" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A369" t="s">
+        <v>10</v>
+      </c>
+      <c r="B369" t="s">
+        <v>79</v>
+      </c>
+      <c r="C369" t="s">
+        <v>63</v>
+      </c>
+      <c r="D369">
+        <v>238</v>
+      </c>
+      <c r="E369">
+        <v>2</v>
+      </c>
+      <c r="F369">
+        <v>39.57</v>
+      </c>
+      <c r="G369">
+        <v>0</v>
+      </c>
+      <c r="H369" s="1">
+        <v>0</v>
+      </c>
+      <c r="I369" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="370" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A370" t="s">
+        <v>10</v>
+      </c>
+      <c r="B370" t="s">
+        <v>79</v>
+      </c>
+      <c r="C370" t="s">
+        <v>63</v>
+      </c>
+      <c r="D370">
+        <v>302</v>
+      </c>
+      <c r="E370">
+        <v>1</v>
+      </c>
+      <c r="F370">
+        <v>26.01</v>
+      </c>
+      <c r="G370">
+        <v>0</v>
+      </c>
+      <c r="H370" s="1">
+        <v>0</v>
+      </c>
+      <c r="I370" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="371" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A371" t="s">
+        <v>10</v>
+      </c>
+      <c r="B371" t="s">
+        <v>79</v>
+      </c>
+      <c r="C371" t="s">
+        <v>63</v>
+      </c>
+      <c r="D371">
+        <v>266</v>
+      </c>
+      <c r="E371">
+        <v>2</v>
+      </c>
+      <c r="F371">
+        <v>25.03</v>
+      </c>
+      <c r="G371">
+        <v>0</v>
+      </c>
+      <c r="H371" s="1">
+        <v>0</v>
+      </c>
+      <c r="I371" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="372" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A372" t="s">
+        <v>10</v>
+      </c>
+      <c r="B372" t="s">
+        <v>79</v>
+      </c>
+      <c r="C372" t="s">
+        <v>63</v>
+      </c>
+      <c r="D372">
+        <v>247</v>
+      </c>
+      <c r="E372">
+        <v>2</v>
+      </c>
+      <c r="F372">
+        <v>42.4</v>
+      </c>
+      <c r="G372">
+        <v>0</v>
+      </c>
+      <c r="H372" s="1">
+        <v>0</v>
+      </c>
+      <c r="I372" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="373" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A373" t="s">
+        <v>10</v>
+      </c>
+      <c r="B373" t="s">
+        <v>80</v>
+      </c>
+      <c r="C373" t="s">
+        <v>52</v>
+      </c>
+      <c r="D373">
+        <v>0</v>
+      </c>
+      <c r="E373">
+        <v>0</v>
+      </c>
+      <c r="F373">
+        <v>0</v>
+      </c>
+      <c r="G373">
+        <v>0</v>
+      </c>
+      <c r="H373" s="1">
+        <v>0</v>
+      </c>
+      <c r="I373" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="374" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A374" t="s">
+        <v>10</v>
+      </c>
+      <c r="B374" t="s">
+        <v>80</v>
+      </c>
+      <c r="C374" t="s">
+        <v>52</v>
+      </c>
+      <c r="D374">
+        <v>0</v>
+      </c>
+      <c r="E374">
+        <v>0</v>
+      </c>
+      <c r="F374">
+        <v>0</v>
+      </c>
+      <c r="G374">
+        <v>0</v>
+      </c>
+      <c r="H374" s="1">
+        <v>0</v>
+      </c>
+      <c r="I374" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="375" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A375" t="s">
+        <v>10</v>
+      </c>
+      <c r="B375" t="s">
+        <v>80</v>
+      </c>
+      <c r="C375" t="s">
+        <v>52</v>
+      </c>
+      <c r="D375">
+        <v>0</v>
+      </c>
+      <c r="E375">
+        <v>0</v>
+      </c>
+      <c r="F375">
+        <v>0</v>
+      </c>
+      <c r="G375">
+        <v>0</v>
+      </c>
+      <c r="H375" s="1">
+        <v>0</v>
+      </c>
+      <c r="I375" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="376" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A376" t="s">
+        <v>10</v>
+      </c>
+      <c r="B376" t="s">
+        <v>80</v>
+      </c>
+      <c r="C376" t="s">
+        <v>52</v>
+      </c>
+      <c r="D376">
+        <v>0</v>
+      </c>
+      <c r="E376">
+        <v>0</v>
+      </c>
+      <c r="F376">
+        <v>0</v>
+      </c>
+      <c r="G376">
+        <v>0</v>
+      </c>
+      <c r="H376" s="1">
+        <v>0</v>
+      </c>
+      <c r="I376" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="377" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A377" t="s">
+        <v>10</v>
+      </c>
+      <c r="B377" t="s">
+        <v>80</v>
+      </c>
+      <c r="C377" t="s">
+        <v>52</v>
+      </c>
+      <c r="D377">
+        <v>0</v>
+      </c>
+      <c r="E377">
+        <v>0</v>
+      </c>
+      <c r="F377">
+        <v>0</v>
+      </c>
+      <c r="G377">
+        <v>0</v>
+      </c>
+      <c r="H377" s="1">
+        <v>0</v>
+      </c>
+      <c r="I377" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="378" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A378" t="s">
+        <v>10</v>
+      </c>
+      <c r="B378" t="s">
+        <v>80</v>
+      </c>
+      <c r="C378" t="s">
+        <v>52</v>
+      </c>
+      <c r="D378">
+        <v>0</v>
+      </c>
+      <c r="E378">
+        <v>0</v>
+      </c>
+      <c r="F378">
+        <v>0</v>
+      </c>
+      <c r="G378">
+        <v>0</v>
+      </c>
+      <c r="H378" s="1">
+        <v>0</v>
+      </c>
+      <c r="I378" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="379" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A379" t="s">
+        <v>10</v>
+      </c>
+      <c r="B379" t="s">
+        <v>80</v>
+      </c>
+      <c r="C379" t="s">
+        <v>52</v>
+      </c>
+      <c r="D379">
+        <v>0</v>
+      </c>
+      <c r="E379">
+        <v>0</v>
+      </c>
+      <c r="F379">
+        <v>0</v>
+      </c>
+      <c r="G379">
+        <v>0</v>
+      </c>
+      <c r="H379" s="1">
+        <v>0</v>
+      </c>
+      <c r="I379" t="s">
         <v>9</v>
       </c>
     </row>
